--- a/artfynd/A 26868-2025 artfynd.xlsx
+++ b/artfynd/A 26868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129741848</v>
       </c>
       <c r="B2" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129741843</v>
       </c>
       <c r="B3" t="n">
-        <v>97642</v>
+        <v>97643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129741844</v>
+        <v>129741849</v>
       </c>
       <c r="B4" t="n">
-        <v>100957</v>
+        <v>97643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,38 +894,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Knarkebo, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506358</v>
+        <v>506365</v>
       </c>
       <c r="R4" t="n">
-        <v>6518826</v>
+        <v>6518733</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -958,11 +954,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>enstaka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129741849</v>
+        <v>129741844</v>
       </c>
       <c r="B5" t="n">
-        <v>97642</v>
+        <v>100958</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,34 +991,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Knarkebo, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506365</v>
+        <v>506358</v>
       </c>
       <c r="R5" t="n">
-        <v>6518733</v>
+        <v>6518826</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1060,6 +1055,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>enstaka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,7 +1089,7 @@
         <v>129741842</v>
       </c>
       <c r="B6" t="n">
-        <v>58594</v>
+        <v>58595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129741850</v>
       </c>
       <c r="B7" t="n">
-        <v>58594</v>
+        <v>58595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26868-2025 artfynd.xlsx
+++ b/artfynd/A 26868-2025 artfynd.xlsx
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129741849</v>
+        <v>129741844</v>
       </c>
       <c r="B4" t="n">
-        <v>97643</v>
+        <v>100958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,34 +894,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Knarkebo, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506365</v>
+        <v>506358</v>
       </c>
       <c r="R4" t="n">
-        <v>6518733</v>
+        <v>6518826</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -954,6 +958,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>enstaka</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129741844</v>
+        <v>129741849</v>
       </c>
       <c r="B5" t="n">
-        <v>100958</v>
+        <v>97643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,38 +1000,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Knarkebo, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506358</v>
+        <v>506365</v>
       </c>
       <c r="R5" t="n">
-        <v>6518826</v>
+        <v>6518733</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1055,11 +1060,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>enstaka</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 26868-2025 artfynd.xlsx
+++ b/artfynd/A 26868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129741848</v>
       </c>
       <c r="B2" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129741843</v>
       </c>
       <c r="B3" t="n">
-        <v>97643</v>
+        <v>97648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129741844</v>
       </c>
       <c r="B4" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129741849</v>
       </c>
       <c r="B5" t="n">
-        <v>97643</v>
+        <v>97648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26868-2025 artfynd.xlsx
+++ b/artfynd/A 26868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129741848</v>
       </c>
       <c r="B2" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129741843</v>
       </c>
       <c r="B3" t="n">
-        <v>97648</v>
+        <v>97652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129741844</v>
       </c>
       <c r="B4" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129741849</v>
       </c>
       <c r="B5" t="n">
-        <v>97648</v>
+        <v>97652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26868-2025 artfynd.xlsx
+++ b/artfynd/A 26868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129741848</v>
       </c>
       <c r="B2" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129741843</v>
       </c>
       <c r="B3" t="n">
-        <v>97652</v>
+        <v>97654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129741844</v>
       </c>
       <c r="B4" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129741849</v>
       </c>
       <c r="B5" t="n">
-        <v>97652</v>
+        <v>97654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26868-2025 artfynd.xlsx
+++ b/artfynd/A 26868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129741848</v>
       </c>
       <c r="B2" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129741843</v>
       </c>
       <c r="B3" t="n">
-        <v>97654</v>
+        <v>97664</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129741844</v>
       </c>
       <c r="B4" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129741849</v>
       </c>
       <c r="B5" t="n">
-        <v>97654</v>
+        <v>97664</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26868-2025 artfynd.xlsx
+++ b/artfynd/A 26868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129741848</v>
       </c>
       <c r="B2" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129741843</v>
       </c>
       <c r="B3" t="n">
-        <v>97664</v>
+        <v>97668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129741844</v>
       </c>
       <c r="B4" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129741849</v>
       </c>
       <c r="B5" t="n">
-        <v>97664</v>
+        <v>97668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>129741842</v>
       </c>
       <c r="B6" t="n">
-        <v>58595</v>
+        <v>58598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129741850</v>
       </c>
       <c r="B7" t="n">
-        <v>58595</v>
+        <v>58598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26868-2025 artfynd.xlsx
+++ b/artfynd/A 26868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129741848</v>
       </c>
       <c r="B2" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129741843</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129741844</v>
       </c>
       <c r="B4" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129741849</v>
       </c>
       <c r="B5" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>129741842</v>
       </c>
       <c r="B6" t="n">
-        <v>58598</v>
+        <v>58601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129741850</v>
       </c>
       <c r="B7" t="n">
-        <v>58598</v>
+        <v>58601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26868-2025 artfynd.xlsx
+++ b/artfynd/A 26868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129741848</v>
       </c>
       <c r="B2" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129741843</v>
       </c>
       <c r="B3" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129741844</v>
       </c>
       <c r="B4" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129741849</v>
       </c>
       <c r="B5" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26868-2025 artfynd.xlsx
+++ b/artfynd/A 26868-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129741848</v>
       </c>
       <c r="B2" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129741843</v>
       </c>
       <c r="B3" t="n">
-        <v>97672</v>
+        <v>97689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129741844</v>
       </c>
       <c r="B4" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>129741849</v>
       </c>
       <c r="B5" t="n">
-        <v>97672</v>
+        <v>97689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>129741842</v>
       </c>
       <c r="B6" t="n">
-        <v>58601</v>
+        <v>58602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129741850</v>
       </c>
       <c r="B7" t="n">
-        <v>58601</v>
+        <v>58602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 26868-2025 artfynd.xlsx
+++ b/artfynd/A 26868-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129741848</v>
+        <v>129741839</v>
       </c>
       <c r="B2" t="n">
-        <v>101019</v>
+        <v>58817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knarkebo, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506363</v>
+        <v>506389</v>
       </c>
       <c r="R2" t="n">
-        <v>6518818</v>
+        <v>6518780</v>
       </c>
       <c r="S2" t="n">
         <v>7</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>En liten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129741843</v>
+        <v>129741842</v>
       </c>
       <c r="B3" t="n">
-        <v>97704</v>
+        <v>58817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,34 +788,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knarkebo, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506376</v>
+        <v>506374</v>
       </c>
       <c r="R3" t="n">
-        <v>6518782</v>
+        <v>6518765</v>
       </c>
       <c r="S3" t="n">
         <v>7</v>
@@ -856,7 +856,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>God förekomst</t>
+          <t>En liten</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129741844</v>
+        <v>129741850</v>
       </c>
       <c r="B4" t="n">
-        <v>101019</v>
+        <v>58817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,26 +894,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506358</v>
+        <v>506319</v>
       </c>
       <c r="R4" t="n">
-        <v>6518826</v>
+        <v>6518669</v>
       </c>
       <c r="S4" t="n">
         <v>7</v>
@@ -962,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>enstaka</t>
+          <t>En liten</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129741849</v>
+        <v>129741838</v>
       </c>
       <c r="B5" t="n">
-        <v>97704</v>
+        <v>97986</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506365</v>
+        <v>506393</v>
       </c>
       <c r="R5" t="n">
-        <v>6518733</v>
+        <v>6518781</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129741842</v>
+        <v>129741843</v>
       </c>
       <c r="B6" t="n">
-        <v>58602</v>
+        <v>97986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1097,38 +1097,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Knarkebo, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506374</v>
+        <v>506376</v>
       </c>
       <c r="R6" t="n">
-        <v>6518765</v>
+        <v>6518782</v>
       </c>
       <c r="S6" t="n">
         <v>7</v>
@@ -1165,7 +1161,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En liten</t>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,10 +1188,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129741850</v>
+        <v>129741849</v>
       </c>
       <c r="B7" t="n">
-        <v>58602</v>
+        <v>97986</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,38 +1199,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208249</v>
+        <v>221946</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Knarkebo, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506319</v>
+        <v>506365</v>
       </c>
       <c r="R7" t="n">
-        <v>6518669</v>
+        <v>6518733</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -1269,11 +1261,6 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>En liten</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1295,6 +1282,320 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129741837</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Knarkebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>506397</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6518782</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>6 plantor</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129741844</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Knarkebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>506358</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6518826</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>enstaka</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129741848</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Knarkebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>506363</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6518818</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hammar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>5 plantor</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26868-2025 artfynd.xlsx
+++ b/artfynd/A 26868-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129741839</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129741842</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129741850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129741838</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129741843</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129741849</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129741837</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129741844</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,8 +1641,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129741848</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>